--- a/Results/Rise_Head/DetectedAction/FindPrincipalComponents_PipelinePCA_Rise_Head/PCA_Dimension_Search_PipelinePCA.xlsx
+++ b/Results/Rise_Head/DetectedAction/FindPrincipalComponents_PipelinePCA_Rise_Head/PCA_Dimension_Search_PipelinePCA.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -585,10 +585,40 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Show Accuracy Threshold</t>
+        </is>
+      </c>
+      <c r="B15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Accuracy Threshold (%)</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Highlight Acceptable Accuracy</t>
+        </is>
+      </c>
+      <c r="B17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Master Path</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>/Users/mohammad/University/Bachelor Project/Final/DetectedActionData/Rise_Head/Master Features/MASTER_Features_Rise_Head.xlsx</t>
         </is>
@@ -885,40 +915,40 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>88.00000000000001</v>
+        <v>89.33333333333333</v>
       </c>
       <c r="C7" t="n">
-        <v>91.15079365079366</v>
+        <v>92.26190476190477</v>
       </c>
       <c r="D7" t="n">
-        <v>87.99999999999999</v>
+        <v>89.33333333333333</v>
       </c>
       <c r="E7" t="n">
-        <v>93.99999999999999</v>
+        <v>94.66666666666666</v>
       </c>
       <c r="F7" t="n">
-        <v>87.25422725422727</v>
+        <v>88.6010286010286</v>
       </c>
       <c r="G7" t="n">
-        <v>87.99999999999999</v>
+        <v>89.33333333333333</v>
       </c>
       <c r="H7" t="n">
-        <v>7.774602526460399</v>
+        <v>9.043106644167022</v>
       </c>
       <c r="I7" t="n">
-        <v>5.411394899597073</v>
+        <v>6.44520677327067</v>
       </c>
       <c r="J7" t="n">
-        <v>7.774602526460401</v>
+        <v>9.043106644167025</v>
       </c>
       <c r="K7" t="n">
-        <v>3.887301263230199</v>
+        <v>4.521553322083512</v>
       </c>
       <c r="L7" t="n">
-        <v>8.397792717192093</v>
+        <v>9.693901542439468</v>
       </c>
       <c r="M7" t="n">
-        <v>7.774602526460401</v>
+        <v>9.043106644167025</v>
       </c>
     </row>
     <row r="8">
@@ -1295,37 +1325,37 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>89.33333333333333</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="C17" t="n">
-        <v>91.52380952380952</v>
+        <v>92.63492063492065</v>
       </c>
       <c r="D17" t="n">
-        <v>89.33333333333333</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="E17" t="n">
-        <v>94.66666666666666</v>
+        <v>95.33333333333334</v>
       </c>
       <c r="F17" t="n">
-        <v>88.43578643578643</v>
+        <v>89.96777296777296</v>
       </c>
       <c r="G17" t="n">
-        <v>89.33333333333333</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="H17" t="n">
         <v>9.043106644167022</v>
       </c>
       <c r="I17" t="n">
-        <v>7.123854794299183</v>
+        <v>7.059192556269112</v>
       </c>
       <c r="J17" t="n">
         <v>9.043106644167025</v>
       </c>
       <c r="K17" t="n">
-        <v>4.521553322083512</v>
+        <v>4.521553322083511</v>
       </c>
       <c r="L17" t="n">
-        <v>9.84042706695085</v>
+        <v>9.876828037179884</v>
       </c>
       <c r="M17" t="n">
         <v>9.043106644167025</v>
@@ -1541,40 +1571,40 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>89.33333333333333</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="C23" t="n">
-        <v>92.03968253968254</v>
+        <v>92.63492063492065</v>
       </c>
       <c r="D23" t="n">
-        <v>89.33333333333333</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="E23" t="n">
-        <v>94.66666666666667</v>
+        <v>95.33333333333334</v>
       </c>
       <c r="F23" t="n">
-        <v>88.34994634994635</v>
+        <v>89.96777296777296</v>
       </c>
       <c r="G23" t="n">
-        <v>89.33333333333333</v>
+        <v>90.66666666666666</v>
       </c>
       <c r="H23" t="n">
-        <v>10.83205120618128</v>
+        <v>9.043106644167022</v>
       </c>
       <c r="I23" t="n">
-        <v>7.858489543081104</v>
+        <v>7.059192556269112</v>
       </c>
       <c r="J23" t="n">
-        <v>10.83205120618128</v>
+        <v>9.043106644167025</v>
       </c>
       <c r="K23" t="n">
-        <v>5.416025603090638</v>
+        <v>4.521553322083511</v>
       </c>
       <c r="L23" t="n">
-        <v>11.91935509680644</v>
+        <v>9.876828037179884</v>
       </c>
       <c r="M23" t="n">
-        <v>10.83205120618128</v>
+        <v>9.043106644167025</v>
       </c>
     </row>
     <row r="24">
@@ -3502,22 +3532,22 @@
         <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="D31" t="n">
-        <v>94.44444444444446</v>
+        <v>100</v>
       </c>
       <c r="E31" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
       <c r="F31" t="n">
-        <v>96.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="G31" t="n">
-        <v>93.26599326599326</v>
+        <v>100</v>
       </c>
       <c r="H31" t="n">
-        <v>93.33333333333333</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32">
@@ -4776,22 +4806,22 @@
         <v>4</v>
       </c>
       <c r="C80" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D80" t="n">
-        <v>88.8888888888889</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E80" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F80" t="n">
-        <v>93.33333333333333</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G80" t="n">
-        <v>85.60606060606061</v>
+        <v>93.26599326599326</v>
       </c>
       <c r="H80" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="81">
@@ -5504,22 +5534,22 @@
         <v>2</v>
       </c>
       <c r="C108" t="n">
-        <v>73.33333333333333</v>
+        <v>80</v>
       </c>
       <c r="D108" t="n">
-        <v>80.83333333333333</v>
+        <v>83.80952380952381</v>
       </c>
       <c r="E108" t="n">
-        <v>73.33333333333334</v>
+        <v>80</v>
       </c>
       <c r="F108" t="n">
-        <v>86.66666666666667</v>
+        <v>90</v>
       </c>
       <c r="G108" t="n">
-        <v>71.35531135531137</v>
+        <v>79.44444444444444</v>
       </c>
       <c r="H108" t="n">
-        <v>73.33333333333334</v>
+        <v>80</v>
       </c>
     </row>
     <row r="109">
@@ -9148,7 +9178,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
         <v>89.96777296777296</v>
@@ -9161,7 +9191,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
         <v>90.66666666666666</v>
@@ -9174,7 +9204,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
         <v>90.66666666666666</v>
